--- a/Input/urbs_intertemporal_2050/2028.xlsx
+++ b/Input/urbs_intertemporal_2050/2028.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\Input\urbs_intertemporal_2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150ECE75-8A4A-4F67-AE3A-C2BE9D9E44F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF456CB8-F629-49F0-AD9F-2E762D1F9A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -1849,6 +1849,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.5546875" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
